--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>89.63320777164668</v>
+        <v>14.56539626289259</v>
       </c>
       <c r="D2" t="n">
-        <v>15.96273239368253</v>
+        <v>2.593944013973412</v>
       </c>
       <c r="E2" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F2" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.5847415610327</v>
+        <v>11.14502050366781</v>
       </c>
       <c r="D3" t="n">
-        <v>22.80350850198276</v>
+        <v>3.705570131572198</v>
       </c>
       <c r="E3" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F3" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.08473143706919</v>
+        <v>9.113768858523745</v>
       </c>
       <c r="D4" t="n">
-        <v>55.16752739666478</v>
+        <v>8.964723201958027</v>
       </c>
       <c r="E4" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F4" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.70941060808197</v>
+        <v>11.49027922381332</v>
       </c>
       <c r="D5" t="n">
-        <v>21.36000936329383</v>
+        <v>3.471001521535247</v>
       </c>
       <c r="E5" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F5" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.93798650958059</v>
+        <v>9.252422807806846</v>
       </c>
       <c r="D6" t="n">
-        <v>56.23874440615446</v>
+        <v>9.138795966000099</v>
       </c>
       <c r="E6" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F6" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.34324442842656</v>
+        <v>6.068277219619316</v>
       </c>
       <c r="D7" t="n">
-        <v>36.42315717162096</v>
+        <v>5.918763040388407</v>
       </c>
       <c r="E7" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F7" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.96465224286918</v>
+        <v>9.094255989466241</v>
       </c>
       <c r="D8" t="n">
-        <v>55.37658097727194</v>
+        <v>8.99869440880669</v>
       </c>
       <c r="E8" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F8" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.90981400466625</v>
+        <v>10.22284477575827</v>
       </c>
       <c r="D9" t="n">
-        <v>49.08601732513135</v>
+        <v>7.976477815333845</v>
       </c>
       <c r="E9" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F9" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.96774378052394</v>
+        <v>2.432258364335141</v>
       </c>
       <c r="D10" t="n">
-        <v>14.05942521373603</v>
+        <v>2.284656597232106</v>
       </c>
       <c r="E10" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F10" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.88383144494823</v>
+        <v>5.181122609804087</v>
       </c>
       <c r="D11" t="n">
-        <v>31.85068141606008</v>
+        <v>5.175735730109764</v>
       </c>
       <c r="E11" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F11" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.09408050842224</v>
+        <v>6.190288082618614</v>
       </c>
       <c r="D12" t="n">
-        <v>38.52941652170457</v>
+        <v>6.261030184776993</v>
       </c>
       <c r="E12" t="n">
-        <v>19.97767057152783</v>
+        <v>3.246371467873273</v>
       </c>
       <c r="F12" t="n">
-        <v>15.42955019657007</v>
+        <v>2.507301906942636</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
